--- a/output/pdf_financials_xlsx/IBAT.xlsx
+++ b/output/pdf_financials_xlsx/IBAT.xlsx
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.210671</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.532384</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>15.756695</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -6410,7 +6410,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -6974,7 +6978,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>5.210671</v>
       </c>

--- a/output/pdf_financials_xlsx/IBAT.xlsx
+++ b/output/pdf_financials_xlsx/IBAT.xlsx
@@ -1281,22 +1281,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.212213</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.336175</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.737</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.186999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1331,22 +1331,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.212213</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.336175</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.737</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>9.186999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.318807</v>
+        <v>0.106594</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.341267</v>
+        <v>0.005092</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.275</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/output/pdf_financials_xlsx/IBAT.xlsx
+++ b/output/pdf_financials_xlsx/IBAT.xlsx
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.677115</v>
+        <v>0.671812</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.384293</v>
+        <v>1.383809</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.077</v>
+        <v>1.076</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.079</v>
+        <v>1.076</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.628</v>
+        <v>1.076</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.085</v>
+        <v>1.076</v>
       </c>
     </row>
     <row r="29">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-13.700385</v>
+        <v>-13.705688</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.571506</v>
+        <v>1.571022</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.423</v>
+        <v>-6.424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.941</v>
+        <v>-15.944</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.404</v>
+        <v>-5.956</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.329</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="30">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-505.6257175660161</v>
+        <v>-683.8117106773823</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2029.878048780488</v>
+        <v>804.8780487804878</v>
       </c>
     </row>
     <row r="31">
@@ -2941,22 +2941,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.671812</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.383809</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.076</v>
       </c>
     </row>
     <row r="101">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">

--- a/output/pdf_financials_xlsx/IBAT.xlsx
+++ b/output/pdf_financials_xlsx/IBAT.xlsx
@@ -2928,7 +2928,7 @@
         <v>-8.51</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.122</v>
+        <v>-3.516</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0.122</v>
@@ -3216,22 +3216,22 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.209706</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-1.297905</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-3.217</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-2.617</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-1.328</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.401</v>
       </c>
     </row>
     <row r="112">
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.00664</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -3815,22 +3815,22 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.209706</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-1.297905</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-3.217</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-2.617</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-1.328</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.401</v>
       </c>
     </row>
     <row r="135">
@@ -3840,22 +3840,22 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.161736</v>
+        <v>-1.371442</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.7687619999999999</v>
+        <v>-2.066667</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-6.209</v>
+        <v>-9.426</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-5.907</v>
+        <v>-8.523999999999999</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-13.455</v>
+        <v>-14.783</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-9.667</v>
+        <v>-10.068</v>
       </c>
     </row>
   </sheetData>
@@ -7122,7 +7122,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7298,7 +7302,11 @@
           <t>Excess of fair value of warrants over proceeds of private placement</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -7698,7 +7706,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7870,7 +7882,11 @@
           <t>Subscription received for private placement</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -9298,7 +9314,11 @@
           <t>Excess of fair value of warrants over proceeds of private Placement</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9530,7 +9550,11 @@
           <t>Subscriptions received for private placement</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -11104,7 +11128,11 @@
           <t>Private placement for acquisition of equipment 34,078 15,978</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -11662,7 +11690,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -12210,7 +12242,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
         <v>-0.209706</v>
       </c>
@@ -12252,7 +12288,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
